--- a/excel/upload4supplier/[FUS]上传订单结算.xlsx
+++ b/excel/upload4supplier/[FUS]上传订单结算.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:R2"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -434,16 +434,37 @@
         <v>发货数量</v>
       </c>
       <c r="H1" s="2" t="str">
-        <v>入库数量</v>
+        <v>出库数量</v>
       </c>
       <c r="I1" s="2" t="str">
+        <v>订单日期</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>订货人</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>接单人</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>接单日期</v>
+      </c>
+      <c r="M1" s="2" t="str">
         <v>拣货人</v>
       </c>
-      <c r="J1" s="2" t="str">
-        <v>结算数量</v>
-      </c>
-      <c r="K1" s="2" t="str">
-        <v>订单日期</v>
+      <c r="N1" s="2" t="str">
+        <v>拣货日期</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>发货人</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>发货日期</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>出库人</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>出库日期</v>
       </c>
     </row>
     <row r="2">
@@ -472,18 +493,39 @@
         <v/>
       </c>
       <c r="I2" s="2" t="str">
-        <v>测试拣货人</v>
+        <v>2026-09-05</v>
       </c>
       <c r="J2" s="2" t="str">
-        <v/>
+        <v>王五</v>
       </c>
       <c r="K2" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <v>2026-09-04</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <v>阿二</v>
+      </c>
+      <c r="N2" s="2" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>测试操作人</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="Q2" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="R2" s="2" t="str">
         <v>2026-09-05</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
   </ignoredErrors>
 </worksheet>
 </file>